--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1009,6 +1009,112 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>132451501</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57945</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>502454</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6642259</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Djupa hackspår i basen av död gran</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1115,6 +1115,498 @@
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>132507997</v>
+      </c>
+      <c r="B6" t="n">
+        <v>58322</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>103015</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Kungsfågel</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Regulus regulus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>502047</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6642001</v>
+      </c>
+      <c r="S6" t="n">
+        <v>25</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Sång från tätt granbestånd</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>132507564</v>
+      </c>
+      <c r="B7" t="n">
+        <v>97966</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>502047</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6642001</v>
+      </c>
+      <c r="S7" t="n">
+        <v>25</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Svårt att uppskatta mera exakt utbredning på platsen.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>132346446</v>
+      </c>
+      <c r="B8" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gillers klack, Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>502497</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6642129</v>
+      </c>
+      <c r="S8" t="n">
+        <v>40</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Äldre gnagspår i död ved</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>132344552</v>
+      </c>
+      <c r="B9" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>502296</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6641945</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>10:59</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -675,48 +675,64 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132349533</v>
+        <v>132507564</v>
       </c>
       <c r="B2" t="n">
-        <v>57945</v>
+        <v>97966</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>221946</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Gillers klack, Gillers klack, Vstm</t>
+          <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502402</v>
+        <v>502047</v>
       </c>
       <c r="R2" t="n">
-        <v>6642019</v>
+        <v>6642001</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +771,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Hackpår i död stående ved</t>
+          <t>Svårt att uppskatta mera exakt utbredning på platsen.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,6 +785,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -787,48 +804,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132346918</v>
+        <v>132346446</v>
       </c>
       <c r="B3" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502486</v>
+        <v>502497</v>
       </c>
       <c r="R3" t="n">
-        <v>6642121</v>
+        <v>6642129</v>
       </c>
       <c r="S3" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,7 +879,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,12 +889,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Hackspår i högstubbe</t>
+          <t>Äldre gnagspår i död ved</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +903,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,45 +922,54 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132351618</v>
+        <v>132344552</v>
       </c>
       <c r="B4" t="n">
-        <v>57945</v>
+        <v>8455</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>106545</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gillers klack, Gillers klack, Vstm</t>
+          <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502588</v>
+        <v>502296</v>
       </c>
       <c r="R4" t="n">
-        <v>6642286</v>
+        <v>6641945</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -969,7 +1001,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,12 +1011,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:49</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Hack lågt på högstubbe av gran</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -993,6 +1020,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,7 +1039,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132451501</v>
+        <v>132349533</v>
       </c>
       <c r="B5" t="n">
         <v>57945</v>
@@ -1040,20 +1068,16 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>502454</v>
+        <v>502402</v>
       </c>
       <c r="R5" t="n">
-        <v>6642259</v>
+        <v>6642019</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1083,14 +1107,24 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>12:54</t>
+        </is>
+      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Djupa hackspår i basen av död gran</t>
+          <t>Hackpår i död stående ved</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1117,27 +1151,27 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132507997</v>
+        <v>132346918</v>
       </c>
       <c r="B6" t="n">
-        <v>58322</v>
+        <v>57945</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1145,36 +1179,20 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502047</v>
+        <v>502486</v>
       </c>
       <c r="R6" t="n">
-        <v>6642001</v>
+        <v>6642121</v>
       </c>
       <c r="S6" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1203,7 +1221,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1213,12 +1231,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Sång från tätt granbestånd</t>
+          <t>Hackspår i högstubbe</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1245,10 +1263,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132507564</v>
+        <v>132507997</v>
       </c>
       <c r="B7" t="n">
-        <v>97966</v>
+        <v>58322</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,35 +1274,35 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221946</v>
+        <v>103015</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr">
         <is>
           <t>observerad</t>
@@ -1346,7 +1364,7 @@
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Svårt att uppskatta mera exakt utbredning på platsen.</t>
+          <t>Sång från tätt granbestånd</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,7 +1373,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1374,53 +1391,52 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132346446</v>
+        <v>132451501</v>
       </c>
       <c r="B8" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillers klack, Gillers klack, Vstm</t>
+          <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502497</v>
+        <v>502454</v>
       </c>
       <c r="R8" t="n">
-        <v>6642129</v>
+        <v>6642259</v>
       </c>
       <c r="S8" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1447,24 +1463,14 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>11:40</t>
-        </is>
-      </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Äldre gnagspår i död ved</t>
+          <t>Djupa hackspår i basen av död gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1473,7 +1479,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1492,54 +1497,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132344552</v>
+        <v>132351618</v>
       </c>
       <c r="B9" t="n">
-        <v>8455</v>
+        <v>57945</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502296</v>
+        <v>502588</v>
       </c>
       <c r="R9" t="n">
-        <v>6641945</v>
+        <v>6642286</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1571,7 +1567,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1581,7 +1577,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>13:49</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Hack lågt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1590,7 +1591,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1607,6 +1607,116 @@
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>132618568</v>
+      </c>
+      <c r="B10" t="n">
+        <v>57136</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>502206</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6641927</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Spillning som bedöms vara max några veckor gammal</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132507564</v>
       </c>
       <c r="B2" t="n">
-        <v>97966</v>
+        <v>97974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>132349533</v>
       </c>
       <c r="B5" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132346918</v>
       </c>
       <c r="B6" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>132507997</v>
       </c>
       <c r="B7" t="n">
-        <v>58322</v>
+        <v>58323</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>132451501</v>
       </c>
       <c r="B8" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>132351618</v>
       </c>
       <c r="B9" t="n">
-        <v>57945</v>
+        <v>57946</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>132618568</v>
       </c>
       <c r="B10" t="n">
-        <v>57136</v>
+        <v>57137</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132507564</v>
       </c>
       <c r="B2" t="n">
-        <v>97974</v>
+        <v>97984</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1042,7 +1042,7 @@
         <v>132349533</v>
       </c>
       <c r="B5" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1154,7 +1154,7 @@
         <v>132346918</v>
       </c>
       <c r="B6" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1266,7 +1266,7 @@
         <v>132507997</v>
       </c>
       <c r="B7" t="n">
-        <v>58323</v>
+        <v>58327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1394,7 +1394,7 @@
         <v>132451501</v>
       </c>
       <c r="B8" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1500,7 +1500,7 @@
         <v>132351618</v>
       </c>
       <c r="B9" t="n">
-        <v>57946</v>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1612,7 +1612,7 @@
         <v>132618568</v>
       </c>
       <c r="B10" t="n">
-        <v>57137</v>
+        <v>57141</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132507564</v>
       </c>
       <c r="B2" t="n">
-        <v>97984</v>
+        <v>97985</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132507564</v>
       </c>
       <c r="B2" t="n">
-        <v>97985</v>
+        <v>97986</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>132946487</v>
       </c>
       <c r="B12" t="n">
-        <v>57145</v>
+        <v>57152</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -1840,7 +1840,7 @@
         <v>132946487</v>
       </c>
       <c r="B12" t="n">
-        <v>57152</v>
+        <v>57162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>

--- a/artfynd/A 11444-2026 artfynd.xlsx
+++ b/artfynd/A 11444-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132507564</v>
+        <v>132618568</v>
       </c>
       <c r="B2" t="n">
-        <v>97998</v>
+        <v>57142</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,50 +686,42 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221946</v>
+        <v>100138</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>502047</v>
+        <v>502206</v>
       </c>
       <c r="R2" t="n">
-        <v>6642001</v>
+        <v>6641927</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -759,24 +751,14 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Svårt att uppskatta mera exakt utbredning på platsen.</t>
+          <t>Spillning som bedöms vara max några veckor gammal</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -785,7 +767,6 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -804,10 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132346446</v>
+        <v>132344552</v>
       </c>
       <c r="B3" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -836,21 +817,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Gillers klack, Gillers klack, Vstm</t>
+          <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>502497</v>
+        <v>502296</v>
       </c>
       <c r="R3" t="n">
-        <v>6642129</v>
+        <v>6641945</v>
       </c>
       <c r="S3" t="n">
-        <v>40</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -879,7 +864,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -889,12 +874,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:40</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Äldre gnagspår i död ved</t>
+          <t>10:59</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -922,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132344552</v>
+        <v>132346918</v>
       </c>
       <c r="B4" t="n">
-        <v>8455</v>
+        <v>57972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,46 +913,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>106545</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>502296</v>
+        <v>502486</v>
       </c>
       <c r="R4" t="n">
-        <v>6641945</v>
+        <v>6642121</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -1001,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1011,7 +982,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>10:59</t>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Hackspår i högstubbe</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1020,7 +996,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1042,11 +1017,11 @@
         <v>132349533</v>
       </c>
       <c r="B5" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1151,14 +1126,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132346918</v>
+        <v>132351618</v>
       </c>
       <c r="B6" t="n">
-        <v>57955</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1186,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>502486</v>
+        <v>502588</v>
       </c>
       <c r="R6" t="n">
-        <v>6642121</v>
+        <v>6642286</v>
       </c>
       <c r="S6" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1221,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1231,12 +1206,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Hackspår i högstubbe</t>
+          <t>Hack lågt på högstubbe av gran</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132507997</v>
+        <v>132451501</v>
       </c>
       <c r="B7" t="n">
-        <v>58332</v>
+        <v>57972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1274,16 +1249,16 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103015</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1291,36 +1266,24 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>502047</v>
+        <v>502454</v>
       </c>
       <c r="R7" t="n">
-        <v>6642001</v>
+        <v>6642259</v>
       </c>
       <c r="S7" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1347,24 +1310,14 @@
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Sång från tätt granbestånd</t>
+          <t>Djupa hackspår i basen av död gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1391,49 +1344,65 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132451501</v>
+        <v>132946487</v>
       </c>
       <c r="B8" t="n">
-        <v>57955</v>
+        <v>57162</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>100138</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>502454</v>
+        <v>502264</v>
       </c>
       <c r="R8" t="n">
-        <v>6642259</v>
+        <v>6642025</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,17 +1429,27 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2026-04-11</t>
+          <t>2026-05-01</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>08:32</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Djupa hackspår i basen av död gran</t>
+          <t>Färska spår av sand- / jordbad bakom en rotvälta, där också en tjäderhöna lämnat en fjäder</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,27 +1476,27 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132351618</v>
+        <v>132507997</v>
       </c>
       <c r="B9" t="n">
-        <v>57955</v>
+        <v>58349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100049</v>
+        <v>103015</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1525,20 +1504,36 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Gillers klack, Gillers klack, Vstm</t>
+          <t>Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>502588</v>
+        <v>502047</v>
       </c>
       <c r="R9" t="n">
-        <v>6642286</v>
+        <v>6642001</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1567,7 +1562,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1577,12 +1572,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:49</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Hack lågt på högstubbe av gran</t>
+          <t>Sång från tätt granbestånd</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1609,10 +1604,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132618568</v>
+        <v>132346446</v>
       </c>
       <c r="B10" t="n">
-        <v>57145</v>
+        <v>8460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1620,45 +1615,42 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Gillers klack, Vstm</t>
+          <t>Gillers klack, Gillers klack, Vstm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>502206</v>
+        <v>502497</v>
       </c>
       <c r="R10" t="n">
-        <v>6641927</v>
+        <v>6642129</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1685,14 +1677,24 @@
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-04-11</t>
         </is>
       </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>11:40</t>
+        </is>
+      </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Spillning som bedöms vara max några veckor gammal</t>
+          <t>Äldre gnagspår i död ved</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,6 +1703,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1722,7 +1725,7 @@
         <v>132948885</v>
       </c>
       <c r="B11" t="n">
-        <v>8455</v>
+        <v>8460</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1837,48 +1840,40 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132946487</v>
+        <v>132946665</v>
       </c>
       <c r="B12" t="n">
-        <v>57162</v>
+        <v>56706</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>206046</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Älg</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alces alces</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
+      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1892,13 +1887,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>502264</v>
+        <v>502280</v>
       </c>
       <c r="R12" t="n">
-        <v>6642025</v>
+        <v>6641985</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1927,7 +1922,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>08:32</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1937,12 +1932,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>08:32</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Färska spår av sand- / jordbad bakom en rotvälta, där också en tjäderhöna lämnat en fjäder</t>
+          <t>08:38</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1966,6 +1956,135 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132507564</v>
+      </c>
+      <c r="B13" t="n">
+        <v>98063</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gillers klack, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>502047</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6642001</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ljusnarsberg</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Svårt att uppskatta mera exakt utbredning på platsen.</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Maria Berdén Evertsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
